--- a/_downloads/2b2c651f96e2032d8353bbb59039724b/data_formats_matrix.xlsx
+++ b/_downloads/2b2c651f96e2032d8353bbb59039724b/data_formats_matrix.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,359 +428,1569 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="119" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>BasicTypes</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Collection</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mapping</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SingleLineComment</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>MultiLineComment</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>SchemaLink</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>"Hello"</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[1, "two", true]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>{"key": "value", "num": 42}</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"Hello"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"two"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>true</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>"key"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"value"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>"num"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>42</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>"\$schema": "http://json-schema.org/draft-07/schema#"</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>"\$schema"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"http://json-schema.org/draft-07/schema#"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>XML</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>&lt;tag&gt;Hello&lt;/tag&gt;</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>&lt;list&gt;
-  &lt;item&gt;1&lt;/item&gt;
-  &lt;item&gt;2&lt;/item&gt;
-&lt;/list&gt;</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>&lt;object&gt;
-  &lt;key&gt;value&lt;/key&gt;
-  &lt;num&gt;42&lt;/num&gt;
-&lt;/object&gt;</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>&lt;element attr="value"&gt;Content&lt;/element&gt;</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>&lt;!-- comment --&gt;</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>&lt;!--
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;tag</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>Hello</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;/tag&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;list</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;item</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;/item&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;item</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;/item&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;/list&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;object</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;key</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>value</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;/key&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>42</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;/num&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;/object&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;element</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>attr=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"value"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>Content</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;/element&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t>&lt;!-- comment --&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t>&lt;!--
   line 1
   line 2
 --&gt;</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>&lt;root xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance"
-      xsi:schemaLocation="http://example.com schema.xsd"&gt;</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>&lt;?xml version="1.0" encoding="UTF-8"?&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;root</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>xmlns:xsi=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"http://www.w3.org/2001/XMLSchema-instance"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+      </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>xsi:schemaLocation=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"http://example.com schema.xsd"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t>&lt;?xml version="1.0" encoding="UTF-8"?&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>YAML</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Hello or 'Hello' or "Hello"</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>- 1
-- two
-- true</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>key: value
-num: 42</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>!!str "value" or !custom { key: val }</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t># comment</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t># line 1
-# line 2</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t># yaml-language-server: \$schema=&lt;url_or_path&gt;</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>%YAML 1.2
----</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>Hello</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>or</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>'Hello'</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>or</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>"Hello"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>two</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>-</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>true</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>key</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>value</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>42</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00902000"/>
+            </rPr>
+            <t>!!str</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>value</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>or</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>!custom</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>{</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>key</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>val</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>}</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t># comment</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t># line 1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t># line 2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t># yaml-language-server: \$schema=&lt;url_or_path&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>%YAML</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>1.2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="000e84b5"/>
+            </rPr>
+            <t>---</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TOML</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>"Hello"</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>key = "value"
-num = 42</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>Hello</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>[</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>,</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>]</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>key</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>value</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>num</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00666666"/>
+            </rPr>
+            <t>=</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>42</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t># comment</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t># line 1
-# line 2</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t># comment</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t># line 1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0060a0b0"/>
+            </rPr>
+            <t># line 2</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Hello or "Hello"</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1,two,true</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Name,Age
-Alice,30</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">Hello or "Hello"
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">1,two,true
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">Name,Age
+Alice,30
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Name,Age,City</t>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">Name,Age,City
+</t>
+          </r>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Fixlength</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Fixed width string (e.g., 'Hello     ')</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Field1Field2Field3</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Pos 1-10: Name, 11-15: Age</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">Fixed width string (e.g., 'Hello     ')
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">Field1Field2Field3
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">Pos 1-10: Name, 11-15: Age
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>H2026052400001</t>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">H2026052400001
+</t>
+          </r>
         </is>
       </c>
     </row>

--- a/_downloads/2b2c651f96e2032d8353bbb59039724b/data_formats_matrix.xlsx
+++ b/_downloads/2b2c651f96e2032d8353bbb59039724b/data_formats_matrix.xlsx
@@ -423,18 +423,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="41" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,40 +448,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>BasicTypes</t>
+          <t>String</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Collection</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Mapping</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>SingleLineComment</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MultiLineComment</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>SchemaLink</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
@@ -513,6 +531,116 @@
           <r>
             <rPr>
               <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>42</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>o</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>r</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="0040a070"/>
+            </rPr>
+            <t>3.14</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>true</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="00007020"/>
+            </rPr>
+            <t>false</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <color rgb="004070a0"/>
+            </rPr>
+            <t>"2026-05-24"</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
             </rPr>
             <t>[</t>
           </r>
@@ -576,7 +704,7 @@
           </r>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -661,22 +789,22 @@
           </r>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -712,7 +840,7 @@
           </r>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -765,6 +893,111 @@
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
+            <t>&lt;tag</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>42</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;/tag&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;tag</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>true</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;/tag&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;tag</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>2026-05-24</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>&lt;/tag&gt;</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
             <t>&lt;list</t>
           </r>
           <r>
@@ -857,7 +1090,7 @@
           </r>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -955,7 +1188,7 @@
           </r>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1009,7 +1242,7 @@
           </r>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1027,7 +1260,7 @@
           </r>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1048,7 +1281,7 @@
           </r>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1110,7 +1343,7 @@
           </r>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1206,6 +1439,105 @@
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
+            <t>42</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>or</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>3.14</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>true</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>false</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>2026-05-24</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
             <t>-</t>
           </r>
           <r>
@@ -1279,7 +1611,7 @@
           </r>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1345,7 +1677,7 @@
           </r>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1468,7 +1800,7 @@
           </r>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1486,7 +1818,7 @@
           </r>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1518,7 +1850,7 @@
           </r>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1536,7 +1868,7 @@
           </r>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1624,6 +1956,117 @@
           <r>
             <rPr>
               <rFont val="Consolas"/>
+            </rPr>
+            <t>42</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>or</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>3</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>14</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>true</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>false</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>2026-05-24</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
               <color rgb="00007020"/>
             </rPr>
             <t>[</t>
@@ -1689,7 +2132,7 @@
           </r>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1785,12 +2228,12 @@
           </r>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1808,7 +2251,7 @@
           </r>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1840,12 +2283,12 @@
           </r>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1874,12 +2317,45 @@
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
+            <t xml:space="preserve">42 or 3.14
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">true / false
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">2026-05-24
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
             <t xml:space="preserve">1,two,true
 </t>
           </r>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1891,27 +2367,27 @@
           </r>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1946,12 +2422,45 @@
             <rPr>
               <rFont val="Consolas"/>
             </rPr>
+            <t xml:space="preserve">Fixed width number (e.g., '00042')
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">Fixed width indicator (e.g., 'Y' / 'N')
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
+            <t xml:space="preserve">Fixed width date (e.g., '20260524')
+</t>
+          </r>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+            </rPr>
             <t xml:space="preserve">Field1Field2Field3
 </t>
           </r>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1962,27 +2471,27 @@
           </r>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <r>
             <rPr>
